--- a/hall/resources/sample/Cumulativebenefits.xlsx
+++ b/hall/resources/sample/Cumulativebenefits.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t>序列ID</t>
   </si>
@@ -199,13 +199,25 @@
     <t>1990000_5000000</t>
   </si>
   <si>
+    <t>任务4</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
+  </si>
+  <si>
+    <t>1990000_20000000</t>
+  </si>
+  <si>
+    <t>1990000_30000000</t>
+  </si>
+  <si>
+    <t>1990000_40000000</t>
+  </si>
+  <si>
     <t>阶段奖励1</t>
   </si>
   <si>
     <t>阶段奖励2</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
   </si>
   <si>
     <t>阶段奖励3</t>
@@ -394,12 +406,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1403,7 +1415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
@@ -1780,33 +1792,39 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="1:6">
       <c r="A20" s="2">
-        <v>2001</v>
+        <v>1016</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4</v>
       </c>
       <c r="E20" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="1:6">
       <c r="A21" s="2">
-        <v>2002</v>
+        <v>1017</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4</v>
       </c>
       <c r="E21" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>33</v>
@@ -1814,19 +1832,94 @@
     </row>
     <row r="22" s="2" customFormat="1" spans="1:6">
       <c r="A22" s="2">
+        <v>1018</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>30000</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:6">
+      <c r="A23" s="2">
+        <v>1019</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="1:6">
+      <c r="A24" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="1:6">
+      <c r="A25" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2">
+        <v>10000</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="1:6">
+      <c r="A26" s="2">
         <v>2003</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="2">
+      <c r="B26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="2">
         <v>2</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E26" s="2">
         <v>100000</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>35</v>
+      <c r="F26" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/Cumulativebenefits.xlsx
+++ b/hall/resources/sample/Cumulativebenefits.xlsx
@@ -1880,6 +1880,7 @@
       <c r="C24" s="2">
         <v>2</v>
       </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="2">
         <v>1000</v>
       </c>
